--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ene-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ene-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>12353.42</v>
+        <v>12037.97</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>157337.59</v>
+        <v>153319.85</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>954.54</v>
+        <v>932.21</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>846.09</v>
+        <v>826.3</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>7969.67</v>
+        <v>7783.24</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2281.16</v>
+        <v>2227.8</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>818.0700000000001</v>
+        <v>806.34</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1827.47</v>
+        <v>1801.28</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3219.05</v>
+        <v>3172.91</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6035.71</v>
+        <v>5949.2</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1846.99</v>
+        <v>1820.52</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>12103.74</v>
+        <v>11930.25</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>12103.74</v>
+        <v>11930.25</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>894.45</v>
+        <v>881.63</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>821.6</v>
+        <v>809.8200000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>8825.59</v>
+        <v>8699.09</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2017.29</v>
+        <v>1988.38</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>926.14</v>
+        <v>914.38</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>7819.08</v>
+        <v>7719.83</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>919.79</v>
+        <v>908.11</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2145.35</v>
+        <v>2118.12</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>790.39</v>
+        <v>779</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>9685.459999999999</v>
+        <v>9545.889999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2855.72</v>
+        <v>2814.57</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1106.38</v>
+        <v>1090.43</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>8248.360000000001</v>
+        <v>8129.5</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5283.52</v>
+        <v>5207.39</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2273.48</v>
+        <v>2240.72</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1525.19</v>
+        <v>1503.21</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>11287.02</v>
+        <v>11124.38</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>5917.37</v>
+        <v>5832.1</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2694.5</v>
+        <v>2659.67</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>792.46</v>
+        <v>782.22</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>18325.47</v>
+        <v>18088.62</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4562.49</v>
+        <v>4503.53</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>4224.8</v>
+        <v>4170.2</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2796.26</v>
+        <v>2760.12</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>78843.28999999999</v>
+        <v>77824.28999999999</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1722.91</v>
+        <v>1700.64</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>6094.01</v>
+        <v>6082</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>4045.41</v>
+        <v>4037.44</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2445.25</v>
+        <v>2440.43</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>4301.13</v>
+        <v>4292.66</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3903.61</v>
+        <v>3895.92</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4359.86</v>
+        <v>4351.27</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1590.18</v>
+        <v>1587.04</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1109.68</v>
+        <v>1107.49</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2695.65</v>
+        <v>2690.34</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>32192.39</v>
+        <v>32192.59</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>20739.79</v>
+        <v>20739.92</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>56736.91</v>
+        <v>56737.28</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>980.24</v>
+        <v>980.25</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1326.44</v>
+        <v>1326.45</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>3478.06</v>
+        <v>3478.08</v>
       </c>
     </row>
     <row r="56">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>4903.3</v>
+        <v>4910.11</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1075.3</v>
+        <v>1076.79</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>6213.87</v>
+        <v>6222.5</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3044.34</v>
+        <v>3048.56</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>10458</v>
+        <v>10472.52</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1776.99</v>
+        <v>1779.46</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3446.89</v>
+        <v>3451.68</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>17461.05</v>
+        <v>17485.29</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>7629.95</v>
+        <v>7624.73</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>4650.31</v>
+        <v>4647.13</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>8147.29</v>
+        <v>8141.73</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2308.26</v>
+        <v>2306.68</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>21538.03</v>
+        <v>21523.32</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1352.07</v>
+        <v>1351.15</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>14073.78</v>
+        <v>14064.16</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3958.51</v>
+        <v>3955.81</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>27385.14</v>
+        <v>27366.43</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>820.24</v>
+        <v>819.6799999999999</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>797.51</v>
+        <v>796.96</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>794.01</v>
+        <v>793.47</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>7268.17</v>
+        <v>7263.2</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>23204.72</v>
+        <v>23125.08</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>7761.17</v>
+        <v>7734.54</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>3881.38</v>
+        <v>3868.06</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3270.89</v>
+        <v>3259.67</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1682.76</v>
+        <v>1676.98</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>988.33</v>
+        <v>984.9400000000001</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>4788.07</v>
+        <v>4771.63</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>4588.76</v>
+        <v>4573.01</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1886.03</v>
+        <v>1879.56</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>15960.62</v>
+        <v>15905.84</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>34077.86</v>
+        <v>33897.85</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>13763.61</v>
+        <v>13690.91</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1627.96</v>
+        <v>1619.36</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>4785.76</v>
+        <v>4760.48</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>5345.78</v>
+        <v>5317.55</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>5564.27</v>
+        <v>5534.88</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>41290.83</v>
+        <v>41072.72</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>9673</v>
+        <v>9621.9</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1920.09</v>
+        <v>1909.95</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1647.81</v>
+        <v>1639.1</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>4443.63</v>
+        <v>4420.15</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>15472.38</v>
+        <v>15390.65</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1687.87</v>
+        <v>1678.96</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>3692.41</v>
+        <v>3672.91</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2015.53</v>
+        <v>2004.88</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>15791.9</v>
+        <v>15708.48</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2180.96</v>
+        <v>2169.44</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>10589.38</v>
+        <v>10533.44</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>954.01</v>
+        <v>948.97</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1069.08</v>
+        <v>1063.43</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>38855.55</v>
+        <v>38612.06</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>820.24</v>
+        <v>815.1</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>3364.93</v>
+        <v>3343.84</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>4565.66</v>
+        <v>4537.05</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>12513.68</v>
+        <v>12435.26</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>4423.09</v>
+        <v>4395.38</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>4047.5</v>
+        <v>4022.14</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2834.83</v>
+        <v>2817.06</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>31785.27</v>
+        <v>31586.09</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>3936.31</v>
+        <v>3911.64</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>9154.200000000001</v>
+        <v>9096.84</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>832.8099999999999</v>
+        <v>827.59</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>848.1799999999999</v>
+        <v>842.86</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>11359.29</v>
+        <v>11288.1</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>8508.700000000001</v>
+        <v>8455.379999999999</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>1061.27</v>
+        <v>1054.62</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>18169.14</v>
+        <v>18055.28</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>15279.44</v>
+        <v>15183.69</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>3813.72</v>
+        <v>3838.72</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1071.28</v>
+        <v>1078.3</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>893.88</v>
+        <v>899.74</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>2467.39</v>
+        <v>2483.56</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>56563.14</v>
+        <v>56933.85</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>791.59</v>
+        <v>796.78</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1601.99</v>
+        <v>1612.48</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>3693.2</v>
+        <v>3717.4</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>7862.52</v>
+        <v>7914.05</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>3059.01</v>
+        <v>3079.06</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1531.98</v>
+        <v>1542.02</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>40220.44</v>
+        <v>40484.04</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2680.82</v>
+        <v>2698.39</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>11349.64</v>
+        <v>11424.03</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1917.82</v>
+        <v>1930.39</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>7076.19</v>
+        <v>7122.56</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>877.11</v>
+        <v>882.86</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>49546.38</v>
+        <v>49871.1</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>42407.99</v>
+        <v>42685.93</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>3616.91</v>
+        <v>3640.61</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1081</v>
+        <v>1088.09</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>6477.73</v>
+        <v>6520.18</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1974.57</v>
+        <v>2001.16</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>3851.39</v>
+        <v>3903.25</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>3214.74</v>
+        <v>3258.03</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2845</v>
+        <v>2883.32</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>52390.07</v>
+        <v>53095.58</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>11004.46</v>
+        <v>11152.65</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>3162.34</v>
+        <v>3204.93</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>7480.09</v>
+        <v>7580.82</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>6024.43</v>
+        <v>6105.55</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>3882.04</v>
+        <v>3934.32</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>7641.07</v>
+        <v>7743.96</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>11370.49</v>
+        <v>11523.61</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1281.04</v>
+        <v>1298.29</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>86384.62</v>
+        <v>87547.91</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>14000.54</v>
+        <v>14189.08</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>41341.45</v>
+        <v>41898.17</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>62057.41</v>
+        <v>62893.1</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1834.95</v>
+        <v>1862.89</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2749.63</v>
+        <v>2791.49</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1157.74</v>
+        <v>1175.36</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>5437.58</v>
+        <v>5520.36</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>868.3</v>
+        <v>881.52</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>1852.38</v>
+        <v>1880.58</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>17076.62</v>
+        <v>17336.6</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>7602.71</v>
+        <v>7718.46</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>1945.23</v>
+        <v>1974.85</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1120.83</v>
+        <v>1137.9</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>2044.21</v>
+        <v>2075.34</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>14713.9</v>
+        <v>14937.9</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>3161.97</v>
+        <v>3210.11</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>2215.55</v>
+        <v>2249.28</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>56966.32</v>
+        <v>57833.58</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>6882.84</v>
+        <v>6987.63</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1634.57</v>
+        <v>1659.46</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>2595.49</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>3984.51</v>
+        <v>4045.17</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3814.69</v>
+        <v>3872.77</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>2613.66</v>
+        <v>2653.45</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>9559.41</v>
+        <v>9704.940000000001</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>10213.62</v>
+        <v>10461.99</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>8716.15</v>
+        <v>8928.1</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>7107.62</v>
+        <v>7280.47</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>41229.92</v>
+        <v>42232.53</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>4065.65</v>
+        <v>4164.52</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>7538.08</v>
+        <v>7721.39</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>2343.41</v>
+        <v>2400.39</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>1130.17</v>
+        <v>1157.65</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>5607.54</v>
+        <v>5743.9</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>23766.88</v>
+        <v>24344.83</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1662.83</v>
+        <v>1703.27</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>11483</v>
+        <v>11762.24</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>983.97</v>
+        <v>1007.9</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1144.63</v>
+        <v>1172.47</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>810.6</v>
+        <v>830.3099999999999</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1195.2</v>
+        <v>1224.26</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>4889.18</v>
+        <v>5008.07</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>10120.58</v>
+        <v>10366.69</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>7638.91</v>
+        <v>7824.67</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>65413.61</v>
+        <v>67004.32000000001</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>13498.76</v>
+        <v>13840.01</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>1176.16</v>
+        <v>1205.89</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>16911.03</v>
+        <v>17338.55</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>861.1</v>
+        <v>882.87</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>4675.7</v>
+        <v>4793.91</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>876.38</v>
+        <v>898.54</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>3164.3</v>
+        <v>3244.29</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>2721.59</v>
+        <v>2790.39</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1989.34</v>
+        <v>2039.63</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>5041.96</v>
+        <v>5169.42</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>5579.96</v>
+        <v>5721.02</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>10951.39</v>
+        <v>11228.24</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>1742.57</v>
+        <v>1786.63</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>7810.15</v>
+        <v>8007.59</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>6962.08</v>
+        <v>7138.08</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>27839.54</v>
+        <v>28543.33</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>4318.63</v>
+        <v>4427.8</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1324.67</v>
+        <v>1364.83</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1017.33</v>
+        <v>1048.18</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>815.9</v>
+        <v>840.64</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>9315.75</v>
+        <v>9598.23</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>18285.32</v>
+        <v>18839.78</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>16773.93</v>
+        <v>17282.57</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>1898.05</v>
+        <v>1955.6</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>5351.48</v>
+        <v>5513.75</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1866.72</v>
+        <v>1923.33</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>8889.67</v>
+        <v>9159.23</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1684.1</v>
+        <v>1735.16</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>4153.97</v>
+        <v>4279.93</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1725.84</v>
+        <v>1778.17</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>944.72</v>
+        <v>973.37</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>5126.45</v>
+        <v>5281.9</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>29951.6</v>
+        <v>30859.83</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>26001.76</v>
+        <v>26790.21</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>2794.42</v>
+        <v>2879.16</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>5195.68</v>
+        <v>5353.23</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>6770.66</v>
+        <v>6975.97</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>2243.25</v>
+        <v>2311.27</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>2621.74</v>
+        <v>2699.66</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>18029.74</v>
+        <v>18565.64</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>5814.72</v>
+        <v>5987.55</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>8059.45</v>
+        <v>8299</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>2914.32</v>
+        <v>3000.94</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>4801.24</v>
+        <v>4943.95</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>794.12</v>
+        <v>817.73</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>1657.18</v>
+        <v>1706.44</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>846.49</v>
+        <v>871.65</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1989.96</v>
+        <v>2049.1</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>822.5599999999999</v>
+        <v>847</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>1386.92</v>
+        <v>1428.14</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>3364.31</v>
+        <v>3464.31</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1325.76</v>
+        <v>1365.16</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>5613.65</v>
+        <v>5780.51</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>6175.48</v>
+        <v>6359.03</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>2181.74</v>
+        <v>2246.59</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>5705.11</v>
+        <v>5874.69</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>7580.15</v>
+        <v>7805.45</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>808.34</v>
+        <v>832.37</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>1185.16</v>
+        <v>1220.38</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1022.41</v>
+        <v>1052.8</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>3626.21</v>
+        <v>3733.99</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ene-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ene-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ene-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ene-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ENERGÍA DEL FUTURO</t>
+          <t>Energía del Futuro</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DIRECCION DE EDUCACION</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DIRECCION DE EDUCACION</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dirección de Educación Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEGURIDAD INDUSTRIAL SPA </t>
+          <t xml:space="preserve">Seguridad Industrial SPA </t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ENERGÍA DEL FUTURO</t>
+          <t>Energía del Futuro</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmería</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cochamó - Salud</t>
+          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DIRECCION DE SEGURIDAD Y OPERACIONES MARITIMAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hospital de Queilen</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEGURIDAD INDUSTRIAL SPA </t>
+          <t xml:space="preserve">Seguridad Industrial SPA </t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEGURIDAD INDUSTRIAL SPA </t>
+          <t xml:space="preserve">Seguridad Industrial SPA </t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmeria</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;AMP; EXPORTADORA UNINNOV EIRL</t>
+          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;amp; EXPORTADORA UNINNOV EIRL</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social Lampa</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmeria</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;AMP; EXPORTADORA UNINNOV EIRL</t>
+          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;amp; EXPORTADORA UNINNOV EIRL</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA ORLANDO ANTONIO</t>
+          <t>Comercializadora orlando antonio</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmería</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>DIRECCION DE SEGURIDAD Y OPERACIONES MARITIMAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13547,7 +13547,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEGURIDAD INDUSTRIAL SPA </t>
+          <t xml:space="preserve">Seguridad Industrial SPA </t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15184,7 +15184,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15916,7 +15916,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Comando de Operaciones Navales</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>CENTRO DE ENTRENAMIENTO DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ene-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ene-2026.xlsx
@@ -562,7 +562,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1493,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1619,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1684,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1810,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2119,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2428,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2493,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3229,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3538,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3603,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4034,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4160,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4286,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4351,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4416,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4603,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4668,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +4916,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5042,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5351,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5660,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5725,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6156,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6465,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6774,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7205,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7270,11 @@
           <t>77.512.806-2</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7396,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7583,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7648,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8079,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8144,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8209,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8518,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8583,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8770,11 @@
           <t>52.003.040-9</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +8835,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10059,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10124,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10189,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10254,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10441,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10506,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +10876,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11124,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11189,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11376,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11624,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +11689,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +11754,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +11941,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12128,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12193,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12380,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12445,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12632,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +12758,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +12945,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13010,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13380,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13445,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +13937,11 @@
           <t>77.787.617-1</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14185,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14494,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14620,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +14685,11 @@
           <t>77.303.388-9</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +14872,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +14937,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15002,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15189,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15376,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15563,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +15872,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +15937,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16002,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16067,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16193,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16319,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16506,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +16571,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +16636,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +16762,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +16888,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +16953,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ene-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ene-2026.xlsx
@@ -13632,7 +13632,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13815,7 +13819,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ene-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ene-2026.xlsx
@@ -4197,7 +4197,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
